--- a/dev/lci-pass_cars.xlsx
+++ b/dev/lci-pass_cars.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C631062A-CCA5-6A48-8C0C-403529B9A3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12580" yWindow="1600" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="passenger cars" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -507,8 +507,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
